--- a/Fourth Semester/static and probability/lab7/lab7.xlsx
+++ b/Fourth Semester/static and probability/lab7/lab7.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER-WIN10\Documents\GitHub\BCE\Fourth Semester\static and probability\lab7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB3EBC78-7DA5-45BC-90DE-960FD55CF9E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86DF32BC-7F0F-402F-8C32-A33B0A6A401C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="21840" windowHeight="13290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="21840" windowHeight="13290" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -56,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
   <si>
     <t>X</t>
   </si>
@@ -134,6 +135,36 @@
   </si>
   <si>
     <t xml:space="preserve"> =SQRT(B32)</t>
+  </si>
+  <si>
+    <t>project</t>
+  </si>
+  <si>
+    <t>profit(rs '000)</t>
+  </si>
+  <si>
+    <t>probability</t>
+  </si>
+  <si>
+    <t>loss(rs '000)</t>
+  </si>
+  <si>
+    <t>profit</t>
+  </si>
+  <si>
+    <t>FORMULA</t>
+  </si>
+  <si>
+    <t>"The maximum expected profit is 19 (rs. `000), which is obtained from project 3. hence we select project 3."</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> =PRODUCT(B19:C19)-PRODUCT(D19:E19)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> =PRODUCT(B20:C20)-PRODUCT(D20:E20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> =PRODUCT(B21:C21)-PRODUCT(D21:E21)</t>
   </si>
 </sst>
 </file>
@@ -703,4 +734,123 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CC1169E-B3EE-43CB-82A2-6F570FF8C65C}">
+  <dimension ref="A18:G24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>1</v>
+      </c>
+      <c r="B19">
+        <v>35</v>
+      </c>
+      <c r="C19">
+        <v>0.5</v>
+      </c>
+      <c r="D19">
+        <v>15</v>
+      </c>
+      <c r="E19">
+        <v>0.5</v>
+      </c>
+      <c r="F19">
+        <f>PRODUCT(B19:C19)-PRODUCT(D19:E19)</f>
+        <v>10</v>
+      </c>
+      <c r="G19" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2</v>
+      </c>
+      <c r="B20">
+        <v>48</v>
+      </c>
+      <c r="C20">
+        <v>0.3</v>
+      </c>
+      <c r="D20">
+        <v>25</v>
+      </c>
+      <c r="E20">
+        <v>0.7</v>
+      </c>
+      <c r="F20">
+        <f>PRODUCT(B20:C20)-PRODUCT(D20:E20)</f>
+        <v>-3.1000000000000014</v>
+      </c>
+      <c r="G20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21">
+        <v>45</v>
+      </c>
+      <c r="C21">
+        <v>0.6</v>
+      </c>
+      <c r="D21">
+        <v>20</v>
+      </c>
+      <c r="E21">
+        <v>0.4</v>
+      </c>
+      <c r="F21">
+        <f>PRODUCT(B21:C21)-PRODUCT(D21:E21)</f>
+        <v>19</v>
+      </c>
+      <c r="G21" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>